--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484639_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484639_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4541</v>
+        <v>5.6627</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8875</v>
+        <v>4.2695</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5666</v>
+        <v>1.3932</v>
       </c>
       <c r="G2" t="n">
         <v>2.0297</v>
@@ -610,13 +610,13 @@
         <v>1.2828</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8459</v>
+        <v>1.0545</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4457</v>
+        <v>0.8277</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4002</v>
+        <v>0.2268</v>
       </c>
       <c r="V2" t="n">
         <v>2.212</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1547</v>
+        <v>5.6439</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8631</v>
+        <v>5.3028</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2915</v>
+        <v>0.3411</v>
       </c>
       <c r="G3" t="n">
         <v>4.9376</v>
@@ -688,13 +688,13 @@
         <v>0.5498</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3327</v>
+        <v>0.1565</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7526</v>
+        <v>-0.313</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4199</v>
+        <v>0.4694</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.244</v>
+        <v>4.8219</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7227</v>
+        <v>3.929</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5213</v>
+        <v>0.8929</v>
       </c>
       <c r="G4" t="n">
         <v>4.2685</v>
@@ -766,13 +766,13 @@
         <v>1.2828</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1746</v>
+        <v>0.7524</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2398</v>
+        <v>-0.0335</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4144</v>
+        <v>0.786</v>
       </c>
       <c r="V4" t="n">
         <v>1.267</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.419</v>
+        <v>4.5079</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3573</v>
+        <v>4.0994</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0617</v>
+        <v>0.4086</v>
       </c>
       <c r="G5" t="n">
         <v>3.8997</v>
@@ -844,13 +844,13 @@
         <v>0.9163</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1428</v>
+        <v>-0.0539</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6795</v>
+        <v>0.0626</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4634</v>
+        <v>-0.1165</v>
       </c>
       <c r="V5" t="n">
         <v>1.5785</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1222</v>
+        <v>1.8493</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4366</v>
+        <v>-1.0407</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5588</v>
+        <v>2.89</v>
       </c>
       <c r="G6" t="n">
         <v>0.4951</v>
@@ -922,13 +922,13 @@
         <v>1.0995</v>
       </c>
       <c r="S6" t="n">
-        <v>3.0382</v>
+        <v>1.7652</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1524</v>
+        <v>0.5483</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8858</v>
+        <v>1.217</v>
       </c>
       <c r="V6" t="n">
         <v>0.3219</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. GARCIA ROYO</t>
+          <t>A. CEJUDO GALAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9776</v>
+        <v>1.7579</v>
       </c>
       <c r="E7" t="n">
-        <v>0.474</v>
+        <v>0.4696</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5036</v>
+        <v>1.2883</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1301</v>
+        <v>2.7507</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6237</v>
+        <v>2.4561</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5063</v>
+        <v>0.2946</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1491</v>
+        <v>1.8323</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9566</v>
+        <v>2.3067</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1925</v>
+        <v>-0.4743</v>
       </c>
       <c r="M7" t="n">
-        <v>0.981</v>
+        <v>0.9184</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3329</v>
+        <v>0.1495</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3139</v>
+        <v>0.7689</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.2986</v>
+        <v>-2.5656</v>
       </c>
       <c r="Q7" t="n">
         <v>-3.6651</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1907</v>
+        <v>0.9496</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7127</v>
+        <v>0.7134</v>
       </c>
       <c r="U7" t="n">
-        <v>0.478</v>
+        <v>0.2362</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9554</v>
+        <v>0.6231</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2774</v>
+        <v>1.5889</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3219</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALAN</t>
+          <t>D. GARCIA ROYO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1338</v>
+        <v>1.5352</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.2545</v>
       </c>
       <c r="F9" t="n">
-        <v>1.214</v>
+        <v>1.2806</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7507</v>
+        <v>3.1301</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4561</v>
+        <v>1.6237</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2946</v>
+        <v>1.5063</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8323</v>
+        <v>2.1491</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3067</v>
+        <v>1.9566</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4743</v>
+        <v>0.1925</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9184</v>
+        <v>0.981</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1495</v>
+        <v>-0.3329</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7689</v>
+        <v>1.3139</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.5656</v>
+        <v>-3.2986</v>
       </c>
       <c r="Q9" t="n">
         <v>-3.6651</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0995</v>
+        <v>0.3665</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3256</v>
+        <v>0.7483</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1637</v>
+        <v>0.4932</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1619</v>
+        <v>0.2551</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6231</v>
+        <v>0.9554</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5889</v>
+        <v>1.2774</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9658</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0003</v>
+        <v>0.2168</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4725</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4728</v>
+        <v>-0.448</v>
       </c>
       <c r="G10" t="n">
         <v>0.6633</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0197</v>
+        <v>0.1974</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0732</v>
+        <v>0.2655</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6439</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0867</v>
+        <v>-0.248</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9874000000000001</v>
+        <v>1.5783</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0741</v>
+        <v>-1.8264</v>
       </c>
       <c r="G11" t="n">
         <v>1.8312</v>
@@ -1312,13 +1312,13 @@
         <v>0.733</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1169</v>
+        <v>-0.2783</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7526</v>
+        <v>-0.1617</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3643</v>
+        <v>-0.1165</v>
       </c>
       <c r="V11" t="n">
         <v>-2.5339</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8716</v>
+        <v>-3.0995</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6808</v>
+        <v>-2.8591</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1908</v>
+        <v>-0.2404</v>
       </c>
       <c r="G12" t="n">
         <v>-0.0324</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2603</v>
+        <v>0.0324</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3288</v>
+        <v>0.1505</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.118</v>
       </c>
       <c r="V12" t="n">
         <v>-1.267</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>23.1473</v>
+        <v>24.2486</v>
       </c>
       <c r="E13" t="n">
-        <v>17.1674</v>
+        <v>18.2686</v>
       </c>
       <c r="F13" t="n">
-        <v>5.979800000000002</v>
+        <v>5.9799</v>
       </c>
       <c r="G13" t="n">
         <v>25.574</v>
@@ -1465,16 +1465,16 @@
         <v>-16.4932</v>
       </c>
       <c r="R13" t="n">
-        <v>7.3302</v>
+        <v>7.330199999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>4.223199999999999</v>
+        <v>5.3241</v>
       </c>
       <c r="T13" t="n">
-        <v>1.452</v>
+        <v>2.553</v>
       </c>
       <c r="U13" t="n">
-        <v>2.7712</v>
+        <v>2.7714</v>
       </c>
       <c r="V13" t="n">
         <v>2.5131</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5631</v>
+        <v>4.4853</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9934</v>
+        <v>3.7626</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5697</v>
+        <v>0.7227</v>
       </c>
       <c r="G14" t="n">
         <v>0.6099</v>
@@ -1546,13 +1546,13 @@
         <v>2.0158</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5966</v>
+        <v>-0.6744</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3582</v>
+        <v>-0.589</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2384</v>
+        <v>-0.0854</v>
       </c>
       <c r="V14" t="n">
         <v>2.5339</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9449</v>
+        <v>0.6549</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9031</v>
+        <v>1.807</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9582000000000001</v>
+        <v>-1.152</v>
       </c>
       <c r="G15" t="n">
         <v>-1.0214</v>
@@ -1624,13 +1624,13 @@
         <v>1.4661</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5002</v>
+        <v>0.2102</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.405</v>
+        <v>-0.5011</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9052</v>
+        <v>0.7113</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1329</v>
+        <v>-0.2037</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1906</v>
+        <v>0.9982</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0577</v>
+        <v>-1.202</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2796</v>
@@ -1702,13 +1702,13 @@
         <v>1.6493</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.2879</v>
       </c>
       <c r="T16" t="n">
-        <v>0.089</v>
+        <v>-0.1033</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5355</v>
+        <v>0.3912</v>
       </c>
       <c r="V16" t="n">
         <v>-0.945</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5089</v>
+        <v>-1.5564</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5954</v>
+        <v>-1.8454</v>
       </c>
       <c r="F17" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.2891</v>
       </c>
       <c r="G17" t="n">
         <v>-2.7084</v>
@@ -1780,13 +1780,13 @@
         <v>1.8326</v>
       </c>
       <c r="S17" t="n">
-        <v>1.312</v>
+        <v>0.2645</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2979</v>
+        <v>0.0479</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0141</v>
+        <v>0.2166</v>
       </c>
       <c r="V17" t="n">
         <v>-0.945</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3713</v>
+        <v>-1.991</v>
       </c>
       <c r="E18" t="n">
         <v>-1.5917</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7796</v>
+        <v>-0.3993</v>
       </c>
       <c r="G18" t="n">
         <v>-0.379</v>
@@ -1858,13 +1858,13 @@
         <v>2.3823</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6519</v>
+        <v>-0.2717</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0761</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5758</v>
+        <v>-0.1955</v>
       </c>
       <c r="V18" t="n">
         <v>-1.89</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.5355</v>
+        <v>-2.6599</v>
       </c>
       <c r="E19" t="n">
-        <v>0.222</v>
+        <v>0.895</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.7575</v>
+        <v>-3.555</v>
       </c>
       <c r="G19" t="n">
         <v>-3.4117</v>
@@ -1936,13 +1936,13 @@
         <v>1.4661</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6186</v>
+        <v>-0.743</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0829</v>
+        <v>-0.4099</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5357</v>
+        <v>-0.3332</v>
       </c>
       <c r="V19" t="n">
         <v>0.945</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0034</v>
+        <v>-3.6959</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5605</v>
+        <v>-2.7528</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4429</v>
+        <v>-0.9431</v>
       </c>
       <c r="G20" t="n">
         <v>-4.9088</v>
@@ -2014,13 +2014,13 @@
         <v>1.8326</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0109</v>
+        <v>0.2966</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2542</v>
+        <v>0.0619</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2651</v>
+        <v>0.2347</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3174</v>
+        <v>-4.4777</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0367</v>
+        <v>-2.3252</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2807</v>
+        <v>-2.1525</v>
       </c>
       <c r="G21" t="n">
         <v>-5.0051</v>
@@ -2092,13 +2092,13 @@
         <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6056</v>
+        <v>-0.7658</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2911</v>
+        <v>0.0027</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-0.7685</v>
       </c>
       <c r="V21" t="n">
         <v>0.0104</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7448</v>
+        <v>-5.1105</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0439</v>
+        <v>-0.2362</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.7009</v>
+        <v>-4.8743</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7732</v>
@@ -2170,13 +2170,13 @@
         <v>0.9163</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1959</v>
+        <v>-0.1699</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1297</v>
+        <v>-0.322</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3256</v>
+        <v>0.1521</v>
       </c>
       <c r="V22" t="n">
         <v>-3.1674</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.307</v>
+        <v>-7.3105</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.4607</v>
+        <v>-4.6915</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8463</v>
+        <v>-2.619</v>
       </c>
       <c r="G23" t="n">
         <v>-6.6967</v>
@@ -2248,13 +2248,13 @@
         <v>1.6493</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.3721</v>
+        <v>-1.3755</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.6516</v>
+        <v>-0.8823</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7205</v>
+        <v>-0.4932</v>
       </c>
       <c r="V23" t="n">
         <v>0.945</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-23.1474</v>
+        <v>-21.8654</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.979800000000001</v>
+        <v>-5.98</v>
       </c>
       <c r="F24" t="n">
-        <v>-17.1676</v>
+        <v>-15.8854</v>
       </c>
       <c r="G24" t="n">
         <v>-25.574</v>
@@ -2326,13 +2326,13 @@
         <v>16.4932</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.223100000000001</v>
+        <v>-2.9411</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.7713</v>
+        <v>-2.7712</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.4518</v>
+        <v>-0.1699</v>
       </c>
       <c r="V24" t="n">
         <v>-2.5131</v>
